--- a/data/S1998_99_FINAL.xlsx
+++ b/data/S1998_99_FINAL.xlsx
@@ -24,8 +24,11 @@
     <sheet name="SERIES" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="CLUBS" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="META" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="TODO" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'TODO'!$A$1:$F$7</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -33,7 +36,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -48,8 +51,12 @@
       <name val="Arial"/>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -71,6 +78,11 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -84,12 +96,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -20903,7 +20921,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20947,6 +20965,88 @@
       <c r="D2" t="inlineStr">
         <is>
           <t>DS-PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1998_99_0138 'Černošice B' prev→CLUB_S1997_98_0034 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1998_99_0433 'Hrušky B' prev→CLUB_S1997_98_0389 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1998_99_0029 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1998_99_0030 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0021</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1998_99_0021 'Baráž o Extraligu' (L15, parent=NODE_S1998_99_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0043</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1998_99_0043 'O postup do I.ligy' (L25, parent=NODE_S1998_99_0037) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
         </is>
       </c>
     </row>
@@ -24586,8 +24686,6 @@
         </is>
       </c>
     </row>
-    <row r="87"/>
-    <row r="88"/>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
@@ -24667,7 +24765,6 @@
         </is>
       </c>
     </row>
-    <row r="96"/>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
@@ -48647,6 +48744,193 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="88" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>typ</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>popis</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>vyřešeno? (ANO/ne)</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>poznámka kolegy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CLUB_S1998_99_0138</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1998_99_0138 'Černošice B' prev→CLUB_S1997_98_0034 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CLUB_S1998_99_0433</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1998_99_0433 'Hrušky B' prev→CLUB_S1997_98_0389 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CLUB_S1998_99_0029</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1998_99_0029 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CLUB_S1998_99_0030</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1998_99_0030 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0021</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1998_99_0021 'Baráž o Extraligu' (L15, parent=NODE_S1998_99_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0043</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1998_99_0043 'O postup do I.ligy' (L25, parent=NODE_S1998_99_0037) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1998_99_FINAL.xlsx
+++ b/data/S1998_99_FINAL.xlsx
@@ -27,7 +27,7 @@
     <sheet name="TODO" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'TODO'!$A$1:$F$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'TODO'!$A$1:$F$46</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20921,7 +20921,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20971,7 +20971,7 @@
     <row r="3">
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1998_99_0138 'Černošice B' prev→CLUB_S1997_98_0034 jen dle jména (město liší) — ověřit (D24)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -20983,7 +20983,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1998_99_0433 'Hrušky B' prev→CLUB_S1997_98_0389 jen dle jména (město liší) — ověřit (D24)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -20995,7 +20995,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1998_99_0029 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -21007,7 +21007,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1998_99_0030 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -21017,14 +21017,9 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>NODE_S1998_99_0021</t>
-        </is>
-      </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1998_99_0021 'Baráž o Extraligu' (L15, parent=NODE_S1998_99_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -21034,17 +21029,490 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>NODE_S1998_99_0043</t>
-        </is>
-      </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1998_99_0043 'O postup do I.ligy' (L25, parent=NODE_S1998_99_0037) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1997_98_0109 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1997_98_0034 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Nový Bydžov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1997_98_0270 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'PJ Steel Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Labská Stamo Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'T. Condo Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1997_98_0389 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Třinec' → 'Český Těšín' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Buly Centrum Kravaře' → 'Kravaře' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NH Válcovny Ostrava' → 'Ostrava' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0029</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  1.kolo'</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0030</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  2.kolo'</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -24686,6 +25154,8 @@
         </is>
       </c>
     </row>
+    <row r="87"/>
+    <row r="88"/>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
@@ -24716,6 +25186,11 @@
           <t>I.ČNHL (12 CZ) + SNHL (12 SVK)</t>
         </is>
       </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0001</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -24728,6 +25203,11 @@
           <t>Kvalifikace o II.ligu</t>
         </is>
       </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0003</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -24740,6 +25220,11 @@
           <t>Krajské přebory (nové velké kraje!)</t>
         </is>
       </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0003</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -24752,6 +25237,11 @@
           <t>I.třída / I.B třída / Krajská soutěž</t>
         </is>
       </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0037</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -24765,6 +25255,7 @@
         </is>
       </c>
     </row>
+    <row r="96"/>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
@@ -26235,12 +26726,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec.</t>
+          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec. || TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>TŽ VŘSR Třinec</t>
+          <t>Třinec</t>
         </is>
       </c>
     </row>
@@ -26319,12 +26810,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -26912,12 +27403,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Chomutov = KLH VT VTJ Chomutov (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **KLH VT VTJ** = post-revolucni nazev (KLH = klub lední hokej, VT = vrcholový tým, VTJ = Vojenská tělovýchovná jednota). city Chomutov.</t>
+          <t>Chomutov = KLH VT VTJ Chomutov (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **KLH VT VTJ** = post-revolucni nazev (KLH = klub lední hokej, VT = vrcholový tým, VTJ = Vojenská tělovýchovná jednota). city Chomutov. || TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>KLH VT VTJ Chomutov</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -27038,12 +27529,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -27374,12 +27865,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem.</t>
+          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem. || TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>NV Ústí nad Labem</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
     </row>
@@ -27962,12 +28453,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Chomutov</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
     </row>
@@ -28051,12 +28542,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří.</t>
+          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří. || TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Klášterec</t>
+          <t>Klášterec nad Ohří</t>
         </is>
       </c>
     </row>
@@ -28088,12 +28579,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Nymburk = NED Hockey Nymburk (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj. Post-revolucni. city Nymburk.</t>
+          <t>Nymburk = NED Hockey Nymburk (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj. Post-revolucni. city Nymburk. || TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>NED Hockey Nymburk</t>
+          <t>Nymburk</t>
         </is>
       </c>
     </row>
@@ -28172,12 +28663,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
     </row>
@@ -28770,12 +29261,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Uherské Hradiště = TJ Slovácká Slavia Uherské Hradiště (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj. **Slovácká** = Moravske Slovacko region. city Uherské Hradiště.</t>
+          <t>Uherské Hradiště = TJ Slovácká Slavia Uherské Hradiště (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj. **Slovácká** = Moravske Slovacko region. city Uherské Hradiště. || TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Slovácká Slavia Uherské Hradiště</t>
+          <t>Uherské Hradiště</t>
         </is>
       </c>
     </row>
@@ -28943,12 +29434,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou.</t>
+          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou. || TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Žďas Žďár nad Sázavou</t>
+          <t>Žďár nad Sázavou</t>
         </is>
       </c>
     </row>
@@ -32380,12 +32871,12 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou.</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>Lokomotiva  Veselí nad Moravou</t>
+          <t>Veselí nad Lužnicí</t>
         </is>
       </c>
     </row>
@@ -32464,12 +32955,12 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -32926,12 +33417,12 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -32968,12 +33459,12 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -33183,12 +33674,12 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>Hluboká nL Vltavou = Tatran Hluboká nL Vltavou (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Ceske Budejovice). city Hluboká nad Vltavou.</t>
+          <t>Hluboká nL Vltavou = Tatran Hluboká nL Vltavou (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Ceske Budejovice). city Hluboká nad Vltavou. || TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>Hluboká</t>
+          <t>Hluboká nad Vltavou</t>
         </is>
       </c>
     </row>
@@ -33277,12 +33768,12 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>Horní Planá = TJ Smrčina Horní Planá (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Český Krumlov). **Smrčina** = pojmenovani po horach Smrciny. city Horní Planá.</t>
+          <t>Horní Planá = TJ Smrčina Horní Planá (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Český Krumlov). **Smrčina** = pojmenovani po horach Smrciny. city Horní Planá. || TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>Smrčina Horní Planá</t>
+          <t>Planá</t>
         </is>
       </c>
     </row>
@@ -33695,12 +34186,12 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -33742,12 +34233,12 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -36765,12 +37256,12 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>Uherské Hradiště = TJ Slovácká Slavia Uherské Hradiště (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj. **Slovácká** = Moravske Slovacko region. city Uherské Hradiště.</t>
+          <t>Uherské Hradiště = TJ Slovácká Slavia Uherské Hradiště (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj. **Slovácká** = Moravske Slovacko region. city Uherské Hradiště. || TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>Slovácká Slavia Uherské Hradiště</t>
+          <t>Uherské Hradiště</t>
         </is>
       </c>
     </row>
@@ -37803,12 +38294,12 @@
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem.</t>
+          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem. || TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>NV Ústí nad Labem</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
     </row>
@@ -38416,12 +38907,12 @@
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Nový Bydžov' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Nový Bydžov</t>
         </is>
       </c>
     </row>
@@ -38495,12 +38986,12 @@
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
     </row>
@@ -38542,12 +39033,12 @@
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>Chomutov</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
     </row>
@@ -40903,12 +41394,12 @@
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t>Pardubice = HC PJ Steel Pardubice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj. **Steel** = ocelarsky sponzor. city Pardubice.</t>
+          <t>Pardubice = HC PJ Steel Pardubice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj. **Steel** = ocelarsky sponzor. city Pardubice. || TBD: city 'PJ Steel Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J338" t="inlineStr">
         <is>
-          <t>PJ Steel Pardubice</t>
+          <t>Pardubice</t>
         </is>
       </c>
     </row>
@@ -41113,12 +41604,12 @@
       </c>
       <c r="I343" t="inlineStr">
         <is>
-          <t>Pardubice = HC Labská Stamo Pardubice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj. **Labská** = Labe reka, **Stamo** = sponzor. city Pardubice.</t>
+          <t>Pardubice = HC Labská Stamo Pardubice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj. **Labská** = Labe reka, **Stamo** = sponzor. city Pardubice. || TBD: city 'Labská Stamo Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J343" t="inlineStr">
         <is>
-          <t>Labská Stamo Pardubice</t>
+          <t>Pardubice</t>
         </is>
       </c>
     </row>
@@ -41197,12 +41688,12 @@
       </c>
       <c r="I345" t="inlineStr">
         <is>
-          <t>Pardubice = HC T.Condo Pardubice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj. Patterns: CONDO Pardubice. city Pardubice.</t>
+          <t>Pardubice = HC T.Condo Pardubice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj. Patterns: CONDO Pardubice. city Pardubice. || TBD: city 'T. Condo Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J345" t="inlineStr">
         <is>
-          <t>T. Condo Pardubice</t>
+          <t>Pardubice</t>
         </is>
       </c>
     </row>
@@ -44799,12 +45290,12 @@
       </c>
       <c r="I426" t="inlineStr">
         <is>
-          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou.</t>
+          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou. || TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J426" t="inlineStr">
         <is>
-          <t>Žďas Žďár nad Sázavou</t>
+          <t>Žďár nad Sázavou</t>
         </is>
       </c>
     </row>
@@ -44940,12 +45431,12 @@
       </c>
       <c r="I429" t="inlineStr">
         <is>
-          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou.</t>
+          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou. || TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J429" t="inlineStr">
         <is>
-          <t>Žďas Žďár nad Sázavou</t>
+          <t>Žďár nad Sázavou</t>
         </is>
       </c>
     </row>
@@ -45442,12 +45933,12 @@
       </c>
       <c r="I440" t="inlineStr">
         <is>
-          <t>A-tým Baník Třinec. Smart fix prev: chybělo → 52/53 0475 (Sokol Železárny VMM Třinec). Identity transition Sokol Železárny VMM → Baník (D28) + zkrácení názvu. || Baník Třinec 53/54 (30_Ostravský). KLÍČOVÝ ROK přejmenování - DSO Baník 1953. Třinec = HC Oceláři Třinec (Wiki D42 - Pavlovo upresneni 04/2026). Genealogie: SK Třinec (1929) -&gt; KS Zaolzie (1938-39, Klub Sportowy Zaolzie - polske obdobi po Mnichove, Zaolzie = ceske uzemi za Olzou) -&gt; SK Železárny Třinec (1939) -&gt; TJ TŽ VŘSR Třinec (1950, VŘSR = Velke rijnove socialisticke revoluce, TŽ = Třinecké železárny) -&gt; TJ TŽ Třinec (1988, vypustil VŘSR) -&gt; HC Železárny Třinec (1994) -&gt; HC Oceláři Třinec (1999-dnes). POZN: Almanach 50/51 'Železárny Molotova Třinec' = TJ TŽ Molotov / VMM = patron Vjaceslav Molotov (nikoli VŘSR jak Wiki) - pravdepodobne kolega zaznamenal jinou variantu nazvu. Patterns: Železárny Molotova Třinec, Sokol Železárny VMM Třinec, Baník Třinec, TŽ Třinec. city Třinec. || Třinec = HC Oceláři Třinec (Wiki D42 - registr ustavy 04/2026). Vsechny trinecke kluby. Hlavni chain: TŽ (Třinecké železárny) Třinec -&gt; Banik Třinec -&gt; Sokol -&gt; Spartak -&gt; Banik -&gt; ZSJ TŽ -&gt; HC Oceláři Třinec. OUPZ Třinec III = paralelni. city Třinec.</t>
+          <t>A-tým Baník Třinec. Smart fix prev: chybělo → 52/53 0475 (Sokol Železárny VMM Třinec). Identity transition Sokol Železárny VMM → Baník (D28) + zkrácení názvu. || Baník Třinec 53/54 (30_Ostravský). KLÍČOVÝ ROK přejmenování - DSO Baník 1953. Třinec = HC Oceláři Třinec (Wiki D42 - Pavlovo upresneni 04/2026). Genealogie: SK Třinec (1929) -&gt; KS Zaolzie (1938-39, Klub Sportowy Zaolzie - polske obdobi po Mnichove, Zaolzie = ceske uzemi za Olzou) -&gt; SK Železárny Třinec (1939) -&gt; TJ TŽ VŘSR Třinec (1950, VŘSR = Velke rijnove socialisticke revoluce, TŽ = Třinecké železárny) -&gt; TJ TŽ Třinec (1988, vypustil VŘSR) -&gt; HC Železárny Třinec (1994) -&gt; HC Oceláři Třinec (1999-dnes). POZN: Almanach 50/51 'Železárny Molotova Třinec' = TJ TŽ Molotov / VMM = patron Vjaceslav Molotov (nikoli VŘSR jak Wiki) - pravdepodobne kolega zaznamenal jinou variantu nazvu. Patterns: Železárny Molotova Třinec, Sokol Železárny VMM Třinec, Baník Třinec, TŽ Třinec. city Třinec. || Třinec = HC Oceláři Třinec (Wiki D42 - registr ustavy 04/2026). Vsechny trinecke kluby. Hlavni chain: TŽ (Třinecké železárny) Třinec -&gt; Banik Třinec -&gt; Sokol -&gt; Spartak -&gt; Banik -&gt; ZSJ TŽ -&gt; HC Oceláři Třinec. OUPZ Třinec III = paralelni. city Třinec. || TBD: city 'Třinec' → 'Český Těšín' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J440" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Český Těšín</t>
         </is>
       </c>
     </row>
@@ -47012,12 +47503,12 @@
       </c>
       <c r="I475" t="inlineStr">
         <is>
-          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice.</t>
+          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice. || TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J475" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Slezan Opava</t>
         </is>
       </c>
     </row>
@@ -47143,12 +47634,12 @@
       </c>
       <c r="I478" t="inlineStr">
         <is>
-          <t>Kravaře = HC Buly Centrum Kravaře (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Opava). city Kravaře.</t>
+          <t>Kravaře = HC Buly Centrum Kravaře (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Opava). city Kravaře. || TBD: city 'Buly Centrum Kravaře' → 'Kravaře' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J478" t="inlineStr">
         <is>
-          <t>Buly Centrum Kravaře</t>
+          <t>Kravaře</t>
         </is>
       </c>
     </row>
@@ -47504,12 +47995,12 @@
       </c>
       <c r="I486" t="inlineStr">
         <is>
-          <t>Ostrava = TJ NH Válcovny Ostrava (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **NH** = Nová huť. **Válcovny** = oddeleni NH. city Ostrava.</t>
+          <t>Ostrava = TJ NH Válcovny Ostrava (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **NH** = Nová huť. **Válcovny** = oddeleni NH. city Ostrava. || TBD: city 'NH Válcovny Ostrava' → 'Ostrava' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J486" t="inlineStr">
         <is>
-          <t>NH Válcovny Ostrava</t>
+          <t>Ostrava</t>
         </is>
       </c>
     </row>
@@ -48754,11 +49245,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="88" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -48803,21 +49294,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S1998_99_0138</t>
+          <t>CLUB_S1998_99_0003</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1998_99_0138 'Černošice B' prev→CLUB_S1997_98_0034 jen dle jména (město liší) — ověřit (D24)</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -48825,21 +49314,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S1998_99_0433</t>
+          <t>CLUB_S1998_99_0005</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1998_99_0433 'Hrušky B' prev→CLUB_S1997_98_0389 jen dle jména (město liší) — ověřit (D24)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -48847,21 +49334,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S1998_99_0029</t>
+          <t>CLUB_S1998_99_0019</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1998_99_0029 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+          <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -48869,21 +49354,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLUB_S1998_99_0030</t>
+          <t>CLUB_S1998_99_0022</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1998_99_0030 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -48891,21 +49374,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NODE_S1998_99_0021</t>
+          <t>CLUB_S1998_99_0030</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1998_99_0021 'Baráž o Extraligu' (L15, parent=NODE_S1998_99_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -48913,24 +49394,802 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NODE_S1998_99_0043</t>
+          <t>CLUB_S1998_99_0047</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1998_99_0043 'O postup do I.ligy' (L25, parent=NODE_S1998_99_0037) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CLUB_S1998_99_0049</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CLUB_S1998_99_0050</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CLUB_S1998_99_0052</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CLUB_S1998_99_0067</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CLUB_S1998_99_0071</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CLUB_S1998_99_0119</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1997_98_0109 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CLUB_S1998_99_0138</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1997_98_0034 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CLUB_S1998_99_0148</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CLUB_S1998_99_0148</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CLUB_S1998_99_0150</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CLUB_S1998_99_0161</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CLUB_S1998_99_0162</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CLUB_S1998_99_0167</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CLUB_S1998_99_0169</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CLUB_S1998_99_0178</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CLUB_S1998_99_0179</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CLUB_S1998_99_0250</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CLUB_S1998_99_0273</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CLUB_S1998_99_0275</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CLUB_S1998_99_0280</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CLUB_S1998_99_0290</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Prostějov' → 'Nový Bydžov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CLUB_S1998_99_0292</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CLUB_S1998_99_0293</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CLUB_S1998_99_0295</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CLUB_S1998_99_0301</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1997_98_0270 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CLUB_S1998_99_0324</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CLUB_S1998_99_0346</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'PJ Steel Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CLUB_S1998_99_0351</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Labská Stamo Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>CLUB_S1998_99_0353</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'T. Condo Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>CLUB_S1998_99_0427</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>CLUB_S1998_99_0433</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1997_98_0389 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>CLUB_S1998_99_0436</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>CLUB_S1998_99_0439</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>CLUB_S1998_99_0451</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Třinec' → 'Český Těšín' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>CLUB_S1998_99_0486</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>CLUB_S1998_99_0489</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Buly Centrum Kravaře' → 'Kravaře' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>CLUB_S1998_99_0497</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'NH Válcovny Ostrava' → 'Ostrava' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>pyramida (feeds_into)</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0029</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL  1.kolo'</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>pyramida (feeds_into)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0030</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL  2.kolo'</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F7"/>
+  <autoFilter ref="A1:F46"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1998_99_FINAL.xlsx
+++ b/data/S1998_99_FINAL.xlsx
@@ -27,7 +27,7 @@
     <sheet name="TODO" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'TODO'!$A$1:$F$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'TODO'!$A$1:$F$35</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -3420,6 +3420,11 @@
           <t>CLUB_S1998_99_0291</t>
         </is>
       </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>CLUB_S1997_98_0252</t>
+        </is>
+      </c>
       <c r="U15" t="inlineStr">
         <is>
           <t>reorganizace</t>
@@ -4452,6 +4457,11 @@
       <c r="Q29" t="inlineStr">
         <is>
           <t>CLUB_S1998_99_0291</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>CLUB_S1997_98_0252</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -20921,7 +20931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D47"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20983,7 +20993,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -20995,7 +21005,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -21007,7 +21017,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -21019,7 +21029,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -21031,7 +21041,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -21043,7 +21053,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -21055,7 +21065,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -21067,7 +21077,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1997_98_0109 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -21079,7 +21089,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1997_98_0034 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -21091,7 +21101,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -21103,7 +21113,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1997_98_0109 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -21115,7 +21125,7 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1997_98_0034 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -21127,7 +21137,7 @@
     <row r="16">
       <c r="C16" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -21139,7 +21149,7 @@
     <row r="17">
       <c r="C17" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -21151,7 +21161,7 @@
     <row r="18">
       <c r="C18" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -21163,7 +21173,7 @@
     <row r="19">
       <c r="C19" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -21175,7 +21185,7 @@
     <row r="20">
       <c r="C20" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -21187,7 +21197,7 @@
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -21199,7 +21209,7 @@
     <row r="22">
       <c r="C22" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: D44 můstek prev_club_id → CLUB_S1997_98_0252 (stejné city+jádro, org. reforma) [fix_d44_bridges]</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -21211,7 +21221,7 @@
     <row r="23">
       <c r="C23" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -21223,7 +21233,7 @@
     <row r="24">
       <c r="C24" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1997_98_0270 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -21235,7 +21245,7 @@
     <row r="25">
       <c r="C25" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -21247,7 +21257,7 @@
     <row r="26">
       <c r="C26" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'PJ Steel Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -21259,7 +21269,7 @@
     <row r="27">
       <c r="C27" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Labská Stamo Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -21271,7 +21281,7 @@
     <row r="28">
       <c r="C28" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'T. Condo Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -21283,7 +21293,7 @@
     <row r="29">
       <c r="C29" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Nový Bydžov' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -21295,7 +21305,7 @@
     <row r="30">
       <c r="C30" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1997_98_0389 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -21307,7 +21317,7 @@
     <row r="31">
       <c r="C31" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -21319,7 +21329,7 @@
     <row r="32">
       <c r="C32" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -21331,7 +21341,7 @@
     <row r="33">
       <c r="C33" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1997_98_0270 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Buly Centrum Kravaře' → 'Kravaře' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -21343,7 +21353,7 @@
     <row r="34">
       <c r="C34" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NH Válcovny Ostrava' → 'Ostrava' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -21353,9 +21363,14 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0029</t>
+        </is>
+      </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'PJ Steel Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  1.kolo'</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -21365,154 +21380,17 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0030</t>
+        </is>
+      </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Labská Stamo Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  2.kolo'</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'T. Condo Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1997_98_0389 (weak, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Třinec' → 'Český Těšín' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Buly Centrum Kravaře' → 'Kravaře' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NH Válcovny Ostrava' → 'Ostrava' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>NODE_S1998_99_0029</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  1.kolo'</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>NODE_S1998_99_0030</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  2.kolo'</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -21529,7 +21407,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K100"/>
+  <dimension ref="A1:L100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21588,6 +21466,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prev_node_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -21630,6 +21513,11 @@
           <t>14 týmů: základ + QF/SF/finále + baráž. Mistr: HC Slovnaft Vsetín (5. titul).</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0001</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -21677,6 +21565,11 @@
           <t>Vítězové 4 skupin II.ligy. Dvoukolově. Top 2 do I.ligy.</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0002</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -21761,6 +21654,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0004</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -21803,6 +21701,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0005</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -21845,6 +21748,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0006</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -21887,6 +21795,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0007</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -21929,6 +21842,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0008</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -21971,6 +21889,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0009</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -22013,6 +21936,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0010</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -22055,6 +21983,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0011</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -22097,6 +22030,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0012</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -22139,6 +22077,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0013</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -22181,6 +22124,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0014</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -22223,6 +22171,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0015</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -22265,6 +22218,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0016</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -22307,6 +22265,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0017</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -22349,6 +22312,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0018</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -22391,6 +22359,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0019</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -22433,6 +22406,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0020</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -22475,6 +22453,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0021</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -22517,6 +22500,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0022</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -22559,6 +22547,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0023</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -22601,6 +22594,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0024</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -22643,6 +22641,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0025</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -22685,6 +22688,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0026</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -22880,6 +22888,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0029</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -23132,6 +23145,11 @@
           <t>II.liga: 2 skupiny + finále + o postup do I.ligy.</t>
         </is>
       </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0032</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -23174,6 +23192,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0033</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -23216,6 +23239,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0034</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -23510,6 +23538,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0039</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -23552,6 +23585,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0040</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -23594,6 +23632,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0041</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -23636,6 +23679,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0042</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -23678,6 +23726,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0043</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -23720,6 +23773,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0044</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -23804,6 +23862,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0045</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -23846,6 +23909,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0046</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -23888,6 +23956,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0047</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -23930,6 +24003,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0048</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -23972,6 +24050,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0049</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -24014,6 +24097,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0050</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -24182,6 +24270,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0054</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -24224,6 +24317,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0055</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -24266,6 +24364,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0056</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -24308,6 +24411,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0057</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -24691,6 +24799,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0060</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -24733,6 +24846,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0061</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -24817,6 +24935,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0062</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -24901,6 +25024,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0064</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -24943,6 +25071,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0065</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -24985,6 +25118,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0066</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -25027,6 +25165,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0067</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -25069,6 +25212,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0069</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -25111,6 +25259,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0070</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -25151,6 +25304,11 @@
       <c r="J86" t="inlineStr">
         <is>
           <t>complete</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0071</t>
         </is>
       </c>
     </row>
@@ -25174,6 +25332,11 @@
           <t>I.liga (10 týmů, jeden stůl)</t>
         </is>
       </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>L10</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -25191,6 +25354,11 @@
           <t>NODE_S1998_99_0001</t>
         </is>
       </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -25208,6 +25376,11 @@
           <t>NODE_S1998_99_0003</t>
         </is>
       </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>L25</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -25225,6 +25398,11 @@
           <t>NODE_S1998_99_0003</t>
         </is>
       </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>L30</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -25242,6 +25420,11 @@
           <t>NODE_S1998_99_0037</t>
         </is>
       </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -25252,6 +25435,11 @@
       <c r="B95" t="inlineStr">
         <is>
           <t>Okresní přebory (jen registr)</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>okresní</t>
         </is>
       </c>
     </row>
@@ -26810,12 +26998,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -28453,12 +28641,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -28663,12 +28851,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Prostějov</t>
         </is>
       </c>
     </row>
@@ -32871,12 +33059,12 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>Veselí nad Lužnicí</t>
+          <t>Veselí nad Moravou</t>
         </is>
       </c>
     </row>
@@ -32955,12 +33143,12 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -33417,12 +33605,12 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -33459,12 +33647,12 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -38907,12 +39095,12 @@
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Nový Bydžov' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>Nový Bydžov</t>
+          <t>Prostějov</t>
         </is>
       </c>
     </row>
@@ -38942,9 +39130,14 @@
           <t>L40</t>
         </is>
       </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>CLUB_S1997_98_0252</t>
+        </is>
+      </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>Jiskra Tepna Náchod (Tepna = závod). Oprava city: "Tepna Náchod" → "Náchod". || Náchod (Wiki - registr ustavy 04/2026). Východocesky/Královéhradecky kraj. city Náchod.</t>
+          <t>Jiskra Tepna Náchod (Tepna = závod). Oprava city: "Tepna Náchod" → "Náchod". || Náchod (Wiki - registr ustavy 04/2026). Východocesky/Královéhradecky kraj. city Náchod. || TBD: D44 můstek prev_club_id → CLUB_S1997_98_0252 (stejné city+jádro, org. reforma) [fix_d44_bridges]</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
@@ -38986,12 +39179,12 @@
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Prostějov</t>
         </is>
       </c>
     </row>
@@ -39033,12 +39226,12 @@
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -45933,12 +46126,12 @@
       </c>
       <c r="I440" t="inlineStr">
         <is>
-          <t>A-tým Baník Třinec. Smart fix prev: chybělo → 52/53 0475 (Sokol Železárny VMM Třinec). Identity transition Sokol Železárny VMM → Baník (D28) + zkrácení názvu. || Baník Třinec 53/54 (30_Ostravský). KLÍČOVÝ ROK přejmenování - DSO Baník 1953. Třinec = HC Oceláři Třinec (Wiki D42 - Pavlovo upresneni 04/2026). Genealogie: SK Třinec (1929) -&gt; KS Zaolzie (1938-39, Klub Sportowy Zaolzie - polske obdobi po Mnichove, Zaolzie = ceske uzemi za Olzou) -&gt; SK Železárny Třinec (1939) -&gt; TJ TŽ VŘSR Třinec (1950, VŘSR = Velke rijnove socialisticke revoluce, TŽ = Třinecké železárny) -&gt; TJ TŽ Třinec (1988, vypustil VŘSR) -&gt; HC Železárny Třinec (1994) -&gt; HC Oceláři Třinec (1999-dnes). POZN: Almanach 50/51 'Železárny Molotova Třinec' = TJ TŽ Molotov / VMM = patron Vjaceslav Molotov (nikoli VŘSR jak Wiki) - pravdepodobne kolega zaznamenal jinou variantu nazvu. Patterns: Železárny Molotova Třinec, Sokol Železárny VMM Třinec, Baník Třinec, TŽ Třinec. city Třinec. || Třinec = HC Oceláři Třinec (Wiki D42 - registr ustavy 04/2026). Vsechny trinecke kluby. Hlavni chain: TŽ (Třinecké železárny) Třinec -&gt; Banik Třinec -&gt; Sokol -&gt; Spartak -&gt; Banik -&gt; ZSJ TŽ -&gt; HC Oceláři Třinec. OUPZ Třinec III = paralelni. city Třinec. || TBD: city 'Třinec' → 'Český Těšín' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>A-tým Baník Třinec. Smart fix prev: chybělo → 52/53 0475 (Sokol Železárny VMM Třinec). Identity transition Sokol Železárny VMM → Baník (D28) + zkrácení názvu. || Baník Třinec 53/54 (30_Ostravský). KLÍČOVÝ ROK přejmenování - DSO Baník 1953. Třinec = HC Oceláři Třinec (Wiki D42 - Pavlovo upresneni 04/2026). Genealogie: SK Třinec (1929) -&gt; KS Zaolzie (1938-39, Klub Sportowy Zaolzie - polske obdobi po Mnichove, Zaolzie = ceske uzemi za Olzou) -&gt; SK Železárny Třinec (1939) -&gt; TJ TŽ VŘSR Třinec (1950, VŘSR = Velke rijnove socialisticke revoluce, TŽ = Třinecké železárny) -&gt; TJ TŽ Třinec (1988, vypustil VŘSR) -&gt; HC Železárny Třinec (1994) -&gt; HC Oceláři Třinec (1999-dnes). POZN: Almanach 50/51 'Železárny Molotova Třinec' = TJ TŽ Molotov / VMM = patron Vjaceslav Molotov (nikoli VŘSR jak Wiki) - pravdepodobne kolega zaznamenal jinou variantu nazvu. Patterns: Železárny Molotova Třinec, Sokol Železárny VMM Třinec, Baník Třinec, TŽ Třinec. city Třinec. || Třinec = HC Oceláři Třinec (Wiki D42 - registr ustavy 04/2026). Vsechny trinecke kluby. Hlavni chain: TŽ (Třinecké železárny) Třinec -&gt; Banik Třinec -&gt; Sokol -&gt; Spartak -&gt; Banik -&gt; ZSJ TŽ -&gt; HC Oceláři Třinec. OUPZ Třinec III = paralelni. city Třinec.</t>
         </is>
       </c>
       <c r="J440" t="inlineStr">
         <is>
-          <t>Český Těšín</t>
+          <t>Třinec</t>
         </is>
       </c>
     </row>
@@ -47503,12 +47696,12 @@
       </c>
       <c r="I475" t="inlineStr">
         <is>
-          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice. || TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice.</t>
         </is>
       </c>
       <c r="J475" t="inlineStr">
         <is>
-          <t>Slezan Opava</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -49245,7 +49438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -49319,12 +49512,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S1998_99_0005</t>
+          <t>CLUB_S1998_99_0019</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -49339,12 +49532,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S1998_99_0019</t>
+          <t>CLUB_S1998_99_0022</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -49359,12 +49552,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLUB_S1998_99_0022</t>
+          <t>CLUB_S1998_99_0030</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -49379,12 +49572,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CLUB_S1998_99_0030</t>
+          <t>CLUB_S1998_99_0049</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -49399,12 +49592,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CLUB_S1998_99_0047</t>
+          <t>CLUB_S1998_99_0050</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -49419,12 +49612,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CLUB_S1998_99_0049</t>
+          <t>CLUB_S1998_99_0067</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -49439,12 +49632,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CLUB_S1998_99_0050</t>
+          <t>CLUB_S1998_99_0071</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -49459,12 +49652,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CLUB_S1998_99_0052</t>
+          <t>CLUB_S1998_99_0119</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1997_98_0109 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -49479,12 +49672,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CLUB_S1998_99_0067</t>
+          <t>CLUB_S1998_99_0138</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1997_98_0034 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -49499,12 +49692,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CLUB_S1998_99_0071</t>
+          <t>CLUB_S1998_99_0148</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -49519,12 +49712,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CLUB_S1998_99_0119</t>
+          <t>CLUB_S1998_99_0167</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1997_98_0109 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -49539,12 +49732,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CLUB_S1998_99_0138</t>
+          <t>CLUB_S1998_99_0169</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1997_98_0034 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -49559,12 +49752,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CLUB_S1998_99_0148</t>
+          <t>CLUB_S1998_99_0178</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -49579,12 +49772,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CLUB_S1998_99_0148</t>
+          <t>CLUB_S1998_99_0179</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -49599,12 +49792,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CLUB_S1998_99_0150</t>
+          <t>CLUB_S1998_99_0250</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -49619,12 +49812,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CLUB_S1998_99_0161</t>
+          <t>CLUB_S1998_99_0273</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
     </row>
@@ -49639,12 +49832,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CLUB_S1998_99_0162</t>
+          <t>CLUB_S1998_99_0275</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -49659,12 +49852,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CLUB_S1998_99_0167</t>
+          <t>CLUB_S1998_99_0280</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
     </row>
@@ -49679,12 +49872,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CLUB_S1998_99_0169</t>
+          <t>CLUB_S1998_99_0291</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: D44 můstek prev_club_id → CLUB_S1997_98_0252 (stejné city+jádro, org. reforma) [fix_d44_bridges]</t>
         </is>
       </c>
     </row>
@@ -49699,12 +49892,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CLUB_S1998_99_0178</t>
+          <t>CLUB_S1998_99_0295</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -49719,12 +49912,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CLUB_S1998_99_0179</t>
+          <t>CLUB_S1998_99_0301</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1997_98_0270 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -49739,12 +49932,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CLUB_S1998_99_0250</t>
+          <t>CLUB_S1998_99_0324</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
         </is>
       </c>
     </row>
@@ -49759,12 +49952,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CLUB_S1998_99_0273</t>
+          <t>CLUB_S1998_99_0346</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>TBD: city 'PJ Steel Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -49779,12 +49972,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CLUB_S1998_99_0275</t>
+          <t>CLUB_S1998_99_0351</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Labská Stamo Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -49799,12 +49992,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CLUB_S1998_99_0280</t>
+          <t>CLUB_S1998_99_0353</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>TBD: city 'T. Condo Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -49819,12 +50012,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CLUB_S1998_99_0290</t>
+          <t>CLUB_S1998_99_0427</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Prostějov' → 'Nový Bydžov' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -49839,12 +50032,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CLUB_S1998_99_0292</t>
+          <t>CLUB_S1998_99_0433</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1997_98_0389 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -49859,12 +50052,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CLUB_S1998_99_0293</t>
+          <t>CLUB_S1998_99_0436</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -49879,12 +50072,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CLUB_S1998_99_0295</t>
+          <t>CLUB_S1998_99_0439</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -49899,12 +50092,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CLUB_S1998_99_0301</t>
+          <t>CLUB_S1998_99_0489</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1997_98_0270 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: city 'Buly Centrum Kravaře' → 'Kravaře' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -49919,12 +50112,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CLUB_S1998_99_0324</t>
+          <t>CLUB_S1998_99_0497</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
+          <t>TBD: city 'NH Válcovny Ostrava' → 'Ostrava' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -49934,17 +50127,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>prev_club_id / identita</t>
+          <t>pyramida (feeds_into)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CLUB_S1998_99_0346</t>
+          <t>NODE_S1998_99_0029</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'PJ Steel Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL  1.kolo'</t>
         </is>
       </c>
     </row>
@@ -49954,242 +50147,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>prev_club_id / identita</t>
+          <t>pyramida (feeds_into)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CLUB_S1998_99_0351</t>
+          <t>NODE_S1998_99_0030</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Labská Stamo Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>CLUB_S1998_99_0353</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'T. Condo Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>CLUB_S1998_99_0427</t>
-        </is>
-      </c>
-      <c r="D37" s="6" t="inlineStr">
-        <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>CLUB_S1998_99_0433</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1997_98_0389 (weak, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>CLUB_S1998_99_0436</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>CLUB_S1998_99_0439</t>
-        </is>
-      </c>
-      <c r="D40" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>CLUB_S1998_99_0451</t>
-        </is>
-      </c>
-      <c r="D41" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Třinec' → 'Český Těšín' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>CLUB_S1998_99_0486</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>CLUB_S1998_99_0489</t>
-        </is>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Buly Centrum Kravaře' → 'Kravaře' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>CLUB_S1998_99_0497</t>
-        </is>
-      </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'NH Válcovny Ostrava' → 'Ostrava' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>pyramida (feeds_into)</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>NODE_S1998_99_0029</t>
-        </is>
-      </c>
-      <c r="D45" s="6" t="inlineStr">
-        <is>
-          <t>top-level kvalifikace bez feeds_into: 'KVAL  1.kolo'</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>pyramida (feeds_into)</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>NODE_S1998_99_0030</t>
-        </is>
-      </c>
-      <c r="D46" s="6" t="inlineStr">
-        <is>
           <t>top-level kvalifikace bez feeds_into: 'KVAL  2.kolo'</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F46"/>
+  <autoFilter ref="A1:F35"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1998_99_FINAL.xlsx
+++ b/data/S1998_99_FINAL.xlsx
@@ -52105,7 +52105,7 @@
         <v>3</v>
       </c>
       <c r="J4" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -52261,7 +52261,7 @@
         <v>9</v>
       </c>
       <c r="J6" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -52417,7 +52417,7 @@
         <v>10</v>
       </c>
       <c r="J8" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -52586,7 +52586,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="M10" t="n">
         <v>40</v>
@@ -52664,7 +52664,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="M11" t="n">
         <v>35</v>
@@ -53032,10 +53032,10 @@
         <v>34</v>
       </c>
       <c r="G16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I16" t="n">
         <v>19</v>
@@ -53052,7 +53052,7 @@
         <v>151</v>
       </c>
       <c r="M16" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -54851,7 +54851,7 @@
         <v>10</v>
       </c>
       <c r="J40" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -54937,7 +54937,7 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M41" t="n">
         <v>47</v>
@@ -55085,7 +55085,7 @@
         <v>15</v>
       </c>
       <c r="J43" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -55093,7 +55093,7 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="M43" t="n">
         <v>41</v>
@@ -55746,7 +55746,7 @@
         <v>27</v>
       </c>
       <c r="J52" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -55754,7 +55754,7 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M52" t="n">
         <v>12</v>

--- a/data/S1998_99_FINAL.xlsx
+++ b/data/S1998_99_FINAL.xlsx
@@ -21407,7 +21407,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L100"/>
+  <dimension ref="A1:N100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21471,6 +21471,16 @@
           <t>prev_node_id</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>entry</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>phase_order</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -25312,8 +25322,6 @@
         </is>
       </c>
     </row>
-    <row r="87"/>
-    <row r="88"/>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
@@ -25443,7 +25451,6 @@
         </is>
       </c>
     </row>
-    <row r="96"/>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>

--- a/data/S1998_99_FINAL.xlsx
+++ b/data/S1998_99_FINAL.xlsx
@@ -21654,6 +21654,16 @@
           <t>NODE_S1998_99_0001</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0010</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0016</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21668,6 +21678,14 @@
         <is>
           <t>NODE_S1997_98_0004</t>
         </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>14 týmů</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -21842,6 +21860,16 @@
           <t>NODE_S1998_99_0007</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0010</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0019</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21856,6 +21884,14 @@
         <is>
           <t>NODE_S1997_98_0008</t>
         </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>horní část ZČ</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -21936,6 +21972,16 @@
           <t>NODE_S1998_99_0007</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0011</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0019</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21950,6 +21996,14 @@
         <is>
           <t>NODE_S1997_98_0010</t>
         </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -21983,6 +22037,16 @@
           <t>NODE_S1998_99_0007</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0015</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0014</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21997,6 +22061,14 @@
         <is>
           <t>NODE_S1997_98_0011</t>
         </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -22030,6 +22102,8 @@
           <t>NODE_S1998_99_0007</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22044,6 +22118,14 @@
         <is>
           <t>NODE_S1997_98_0012</t>
         </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (dolní)</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -22077,6 +22159,8 @@
           <t>NODE_S1998_99_0007</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22091,6 +22175,14 @@
         <is>
           <t>NODE_S1997_98_0013</t>
         </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (horní)</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -22124,6 +22216,8 @@
           <t>NODE_S1998_99_0007</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22138,6 +22232,14 @@
         <is>
           <t>NODE_S1997_98_0014</t>
         </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -22171,6 +22273,8 @@
           <t>NODE_S1998_99_0007</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22185,6 +22289,14 @@
         <is>
           <t>NODE_S1997_98_0015</t>
         </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -22218,6 +22330,8 @@
           <t>NODE_S1998_99_0001</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22232,6 +22346,14 @@
         <is>
           <t>NODE_S1997_98_0016</t>
         </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -22265,6 +22387,8 @@
           <t>NODE_S1998_99_0007</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22279,6 +22403,14 @@
         <is>
           <t>NODE_S1997_98_0017</t>
         </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -22312,6 +22444,8 @@
           <t>NODE_S1998_99_0007</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22326,6 +22460,14 @@
         <is>
           <t>NODE_S1997_98_0018</t>
         </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>o 9. místo</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -22359,6 +22501,16 @@
           <t>NODE_S1998_99_0007</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0013</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0012</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22373,6 +22525,14 @@
         <is>
           <t>NODE_S1997_98_0019</t>
         </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>poražení ČF</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -22500,6 +22660,16 @@
           <t>NODE_S1998_99_0003</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0023</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0027</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22514,6 +22684,14 @@
         <is>
           <t>NODE_S1997_98_0022</t>
         </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>14 týmů</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -22547,6 +22725,16 @@
           <t>NODE_S1998_99_0003</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0024</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0027</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22561,6 +22749,14 @@
         <is>
           <t>NODE_S1997_98_0023</t>
         </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>střed tabulky ZČ</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -22594,6 +22790,12 @@
           <t>NODE_S1998_99_0003</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0025</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22608,6 +22810,14 @@
         <is>
           <t>NODE_S1997_98_0024</t>
         </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>horní ZČ + postupující z předkola</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -22641,6 +22851,12 @@
           <t>NODE_S1998_99_0003</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0026</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22655,6 +22871,14 @@
         <is>
           <t>NODE_S1997_98_0025</t>
         </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -22688,6 +22912,8 @@
           <t>NODE_S1998_99_0003</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22702,6 +22928,14 @@
         <is>
           <t>NODE_S1997_98_0026</t>
         </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="28">
@@ -22735,6 +22969,8 @@
           <t>NODE_S1998_99_0003</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22744,6 +22980,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>11.–14. ZČ</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -23019,6 +23263,8 @@
           <t>NODE_S1998_99_0031</t>
         </is>
       </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23028,6 +23274,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>9 týmů</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -23103,6 +23357,8 @@
           <t>NODE_S1998_99_0031</t>
         </is>
       </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23112,6 +23368,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N37" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="38">
@@ -23286,6 +23550,12 @@
           <t>NODE_S1998_99_0037</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0041</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23295,6 +23565,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -23328,6 +23606,12 @@
           <t>NODE_S1998_99_0037</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0042</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23337,6 +23621,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="43">
@@ -23370,6 +23662,8 @@
           <t>NODE_S1998_99_0037</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23379,6 +23673,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="44">
@@ -23496,6 +23798,8 @@
           <t>NODE_S1998_99_0037</t>
         </is>
       </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23505,6 +23809,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -23679,6 +23991,12 @@
           <t>NODE_S1998_99_0047</t>
         </is>
       </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0051</t>
+        </is>
+      </c>
       <c r="I50" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23693,6 +24011,14 @@
         <is>
           <t>NODE_S1997_98_0042</t>
         </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>8 týmů</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -23773,6 +24099,8 @@
           <t>NODE_S1998_99_0047</t>
         </is>
       </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23787,6 +24115,14 @@
         <is>
           <t>NODE_S1997_98_0044</t>
         </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>5.–8. ZČ</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -24458,6 +24794,12 @@
           <t>NODE_S1998_99_0064</t>
         </is>
       </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0068</t>
+        </is>
+      </c>
       <c r="I67" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24467,6 +24809,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>12 týmů</t>
+        </is>
+      </c>
+      <c r="N67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -24542,6 +24892,8 @@
           <t>NODE_S1998_99_0064</t>
         </is>
       </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24551,6 +24903,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>7.–12. ZČ</t>
+        </is>
+      </c>
+      <c r="N69" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="70">
@@ -24935,6 +25295,16 @@
           <t>NODE_S1998_99_0075</t>
         </is>
       </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0078</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0079</t>
+        </is>
+      </c>
       <c r="I78" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24949,6 +25319,14 @@
         <is>
           <t>NODE_S1997_98_0062</t>
         </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>10 týmů</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -24982,6 +25360,8 @@
           <t>NODE_S1998_99_0075</t>
         </is>
       </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24991,6 +25371,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="80">
@@ -25024,6 +25412,8 @@
           <t>NODE_S1998_99_0075</t>
         </is>
       </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25038,6 +25428,14 @@
         <is>
           <t>NODE_S1997_98_0064</t>
         </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>5.–10. ZČ</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="81">
@@ -25322,6 +25720,8 @@
         </is>
       </c>
     </row>
+    <row r="87"/>
+    <row r="88"/>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
@@ -25451,6 +25851,7 @@
         </is>
       </c>
     </row>
+    <row r="96"/>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>

--- a/data/S1998_99_FINAL.xlsx
+++ b/data/S1998_99_FINAL.xlsx
@@ -753,6 +753,11 @@
           <t>HC Slovnaft Vsetín (C)</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="F5" t="n">
         <v>52</v>
       </c>
@@ -22102,8 +22107,6 @@
           <t>NODE_S1998_99_0007</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22159,8 +22162,6 @@
           <t>NODE_S1998_99_0007</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22216,8 +22217,6 @@
           <t>NODE_S1998_99_0007</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22273,8 +22272,6 @@
           <t>NODE_S1998_99_0007</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22330,8 +22327,6 @@
           <t>NODE_S1998_99_0001</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22387,8 +22382,6 @@
           <t>NODE_S1998_99_0007</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22444,8 +22437,6 @@
           <t>NODE_S1998_99_0007</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22795,7 +22786,6 @@
           <t>NODE_S1998_99_0025</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22856,7 +22846,6 @@
           <t>NODE_S1998_99_0026</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22912,8 +22901,6 @@
           <t>NODE_S1998_99_0003</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22969,8 +22956,6 @@
           <t>NODE_S1998_99_0003</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23263,8 +23248,6 @@
           <t>NODE_S1998_99_0031</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23357,8 +23340,6 @@
           <t>NODE_S1998_99_0031</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23555,7 +23536,6 @@
           <t>NODE_S1998_99_0041</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23611,7 +23591,6 @@
           <t>NODE_S1998_99_0042</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23662,8 +23641,6 @@
           <t>NODE_S1998_99_0037</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23798,8 +23775,6 @@
           <t>NODE_S1998_99_0037</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23991,7 +23966,6 @@
           <t>NODE_S1998_99_0047</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
           <t>NODE_S1998_99_0051</t>
@@ -24099,8 +24073,6 @@
           <t>NODE_S1998_99_0047</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24794,7 +24766,6 @@
           <t>NODE_S1998_99_0064</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
           <t>NODE_S1998_99_0068</t>
@@ -24892,8 +24863,6 @@
           <t>NODE_S1998_99_0064</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25360,8 +25329,6 @@
           <t>NODE_S1998_99_0075</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25412,8 +25379,6 @@
           <t>NODE_S1998_99_0075</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25720,8 +25685,6 @@
         </is>
       </c>
     </row>
-    <row r="87"/>
-    <row r="88"/>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
@@ -25851,7 +25814,6 @@
         </is>
       </c>
     </row>
-    <row r="96"/>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
@@ -49652,7 +49614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49832,6 +49794,18 @@
       <c r="B15" t="inlineStr">
         <is>
           <t>1 oprav kvalifikačních levelů. Sloupec Q (level) aktualizován.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>mistr</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>HC Slovnaft Vsetín</t>
         </is>
       </c>
     </row>

--- a/data/S1998_99_FINAL.xlsx
+++ b/data/S1998_99_FINAL.xlsx
@@ -25685,6 +25685,8 @@
         </is>
       </c>
     </row>
+    <row r="87"/>
+    <row r="88"/>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
@@ -25814,6 +25816,7 @@
         </is>
       </c>
     </row>
+    <row r="96"/>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
